--- a/data/dividends_info_20260722.xlsx
+++ b/data/dividends_info_20260722.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>57.09000015258789</v>
+        <v>58.27000045776367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1576458219643573</v>
+        <v>0.1544534053423175</v>
       </c>
       <c r="J2" t="n">
         <v>236</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.25</v>
+        <v>65.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0727969348659</v>
+        <v>1.068702290076336</v>
       </c>
       <c r="J3" t="n">
         <v>215</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.239999771118164</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6493506654355597</v>
+        <v>0.6651884363083036</v>
       </c>
       <c r="J4" t="n">
         <v>145</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8333333519597853</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J5" t="n">
         <v>145</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>57.11000061035156</v>
+        <v>58.27000045776367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1575906129191792</v>
+        <v>0.1544534053423175</v>
       </c>
       <c r="J6" t="n">
         <v>145</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.045000076293945</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I7" t="n">
-        <v>3.765281033120711</v>
+        <v>3.737864181496264</v>
       </c>
       <c r="J7" t="n">
         <v>124</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.36499977111816</v>
+        <v>22.30500030517578</v>
       </c>
       <c r="I8" t="n">
-        <v>1.207243473119432</v>
+        <v>1.21049090475622</v>
       </c>
       <c r="J8" t="n">
         <v>124</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.039999961853027</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I9" t="n">
-        <v>3.311258299058689</v>
+        <v>3.278688575849199</v>
       </c>
       <c r="J9" t="n">
         <v>117</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.400000095367432</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8108108003614941</v>
+        <v>0.8053691481358354</v>
       </c>
       <c r="J10" t="n">
         <v>89</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8333333519597853</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J11" t="n">
         <v>89</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.36499977111816</v>
+        <v>22.30500030517578</v>
       </c>
       <c r="I14" t="n">
-        <v>1.207243473119432</v>
+        <v>1.21049090475622</v>
       </c>
       <c r="J14" t="n">
         <v>61</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>57.11000061035156</v>
+        <v>58.27000045776367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1575906129191792</v>
+        <v>0.1544534053423175</v>
       </c>
       <c r="J15" t="n">
         <v>61</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>91</v>
+        <v>92.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.461538461538462</v>
+        <v>1.437837837837838</v>
       </c>
       <c r="J16" t="n">
         <v>61</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.460000038146973</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="I17" t="n">
-        <v>5.494505456117444</v>
+        <v>5.415162492161021</v>
       </c>
       <c r="J17" t="n">
         <v>54</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8333333519597853</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J18" t="n">
         <v>33</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.759999990463257</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="I19" t="n">
-        <v>7.971014520296202</v>
+        <v>7.586206647076882</v>
       </c>
       <c r="J19" t="n">
         <v>19</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.869999885559082</v>
+        <v>2.829999923706055</v>
       </c>
       <c r="I21" t="n">
-        <v>5.155714491297804</v>
+        <v>5.228586713395586</v>
       </c>
       <c r="J21" t="n">
         <v>12</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.900000095367432</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I22" t="n">
-        <v>4.237288067101817</v>
+        <v>4.230118552532127</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.170000076293945</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="I23" t="n">
-        <v>3.357314087255939</v>
+        <v>3.381642621134783</v>
       </c>
       <c r="J23" t="n">
         <v>-2</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9.991999626159668</v>
+        <v>10.03600025177002</v>
       </c>
       <c r="I24" t="n">
-        <v>2.60208176268646</v>
+        <v>2.590673510138111</v>
       </c>
       <c r="J24" t="n">
         <v>-2</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.42000007629395</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="I25" t="n">
-        <v>4.470938871750703</v>
+        <v>4.405286380627387</v>
       </c>
       <c r="J25" t="n">
         <v>-2</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.584000110626221</v>
+        <v>2.621999979019165</v>
       </c>
       <c r="I26" t="n">
-        <v>8.513931524046413</v>
+        <v>8.390541638459409</v>
       </c>
       <c r="J26" t="n">
         <v>-2</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8333333519597853</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J27" t="n">
         <v>-2</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6.650000095367432</v>
+        <v>6.554999828338623</v>
       </c>
       <c r="I28" t="n">
-        <v>3.609022504634104</v>
+        <v>3.661327327003584</v>
       </c>
       <c r="J28" t="n">
         <v>-2</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>19</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I29" t="n">
-        <v>1.978947368421053</v>
+        <v>1.989418029571574</v>
       </c>
       <c r="J29" t="n">
         <v>-2</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.960000038146973</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="I33" t="n">
-        <v>5.067567502259338</v>
+        <v>5.172413623006964</v>
       </c>
       <c r="J33" t="n">
         <v>-9</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.119999885559082</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I34" t="n">
-        <v>4.009434178699683</v>
+        <v>3.971962422114281</v>
       </c>
       <c r="J34" t="n">
         <v>-16</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.590000152587891</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="I35" t="n">
-        <v>1.525054415532715</v>
+        <v>1.548672572906767</v>
       </c>
       <c r="J35" t="n">
         <v>-16</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>33.40000152587891</v>
+        <v>33.54999923706055</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4491017758899722</v>
+        <v>0.4470938998839218</v>
       </c>
       <c r="J36" t="n">
         <v>-16</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9.600000381469727</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="I37" t="n">
-        <v>23.25937407575551</v>
+        <v>23.13886101831865</v>
       </c>
       <c r="J37" t="n">
         <v>-16</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.199999809265137</v>
+        <v>5.25</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J38" t="n">
         <v>-23</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>22.36000061035156</v>
+        <v>22.34000015258789</v>
       </c>
       <c r="I39" t="n">
-        <v>4.248658202451915</v>
+        <v>4.252461922610824</v>
       </c>
       <c r="J39" t="n">
         <v>-30</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>27.89999961853027</v>
+        <v>27.79999923706055</v>
       </c>
       <c r="I40" t="n">
-        <v>0.698924740739019</v>
+        <v>0.7014388681710571</v>
       </c>
       <c r="J40" t="n">
         <v>-30</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>4.961999893188477</v>
       </c>
       <c r="I42" t="n">
-        <v>5.8</v>
+        <v>5.844417699365408</v>
       </c>
       <c r="J42" t="n">
         <v>-30</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.915999889373779</v>
+        <v>3.926000118255615</v>
       </c>
       <c r="I43" t="n">
-        <v>4.085801954033919</v>
+        <v>4.07539468111607</v>
       </c>
       <c r="J43" t="n">
         <v>-30</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.621999979019165</v>
+        <v>2.614000082015991</v>
       </c>
       <c r="I44" t="n">
-        <v>5.286041232229428</v>
+        <v>5.302218655368509</v>
       </c>
       <c r="J44" t="n">
         <v>-30</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>51.2400016784668</v>
+        <v>51.15999984741211</v>
       </c>
       <c r="I45" t="n">
-        <v>1.229508156446358</v>
+        <v>1.231430808989473</v>
       </c>
       <c r="J45" t="n">
         <v>-30</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.199999809265137</v>
+        <v>6.159999847412109</v>
       </c>
       <c r="I46" t="n">
-        <v>2.258064585595426</v>
+        <v>2.272727329024459</v>
       </c>
       <c r="J46" t="n">
         <v>-30</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>27.44000053405762</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="I48" t="n">
-        <v>3.097667578194863</v>
+        <v>3.085299540976289</v>
       </c>
       <c r="J48" t="n">
         <v>-30</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>57.11000061035156</v>
+        <v>58.27000045776367</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1575906129191792</v>
+        <v>0.1544534053423175</v>
       </c>
       <c r="J49" t="n">
         <v>-30</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.490000009536743</v>
+        <v>1.5</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6711409353016787</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="J50" t="n">
         <v>-30</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>6.22599983215332</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="I51" t="n">
-        <v>2.91198208942604</v>
+        <v>2.928917581971889</v>
       </c>
       <c r="J51" t="n">
         <v>-30</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9.350000381469727</v>
+        <v>9.430000305175781</v>
       </c>
       <c r="I52" t="n">
-        <v>2.780748549650119</v>
+        <v>2.757157917134907</v>
       </c>
       <c r="J52" t="n">
         <v>-30</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>10.28499984741211</v>
+        <v>10.32499980926514</v>
       </c>
       <c r="I53" t="n">
-        <v>2.693242626247566</v>
+        <v>2.682808766266844</v>
       </c>
       <c r="J53" t="n">
         <v>-30</v>
@@ -4071,7 +4071,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4234,14 +4234,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4268,14 +4268,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4336,14 +4336,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4387,14 +4387,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4404,14 +4404,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4428,7 +4428,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4438,14 +4438,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4523,14 +4523,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4547,7 +4547,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4574,14 +4574,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4632,7 +4632,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4642,14 +4642,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4734,7 +4734,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4744,14 +4744,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4778,14 +4778,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4795,14 +4795,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4819,7 +4819,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4846,14 +4846,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4921,7 +4921,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4931,14 +4931,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4955,7 +4955,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4965,14 +4965,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5006,7 +5006,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5023,7 +5023,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5091,7 +5091,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5152,14 +5152,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5186,14 +5186,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5203,14 +5203,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5237,14 +5237,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5254,14 +5254,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5295,7 +5295,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5322,14 +5322,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5339,14 +5339,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5390,14 +5390,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5424,14 +5424,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5441,14 +5441,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5458,14 +5458,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5482,7 +5482,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5509,14 +5509,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5560,14 +5560,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5577,14 +5577,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5594,14 +5594,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5703,7 +5703,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5747,14 +5747,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5805,7 +5805,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5815,14 +5815,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5941,7 +5941,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5992,7 +5992,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6002,14 +6002,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6026,7 +6026,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6036,14 +6036,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6094,7 +6094,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6111,7 +6111,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6128,7 +6128,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6145,7 +6145,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6162,7 +6162,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6179,7 +6179,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6196,7 +6196,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6213,7 +6213,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6257,14 +6257,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6281,7 +6281,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6298,7 +6298,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6315,7 +6315,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6325,14 +6325,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6349,7 +6349,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6366,7 +6366,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6393,14 +6393,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6410,14 +6410,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6495,14 +6495,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6519,7 +6519,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6536,7 +6536,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6614,14 +6614,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6631,14 +6631,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6648,14 +6648,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6665,14 +6665,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6727,44 +6727,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>